--- a/Data/itinerary.xlsx
+++ b/Data/itinerary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkko\Desktop\TI xls 260529\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkko\Desktop\TI xls 260529\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B43DD5-DE37-4E8B-860B-04CC42F1CCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A288DB95-7E69-48C2-8D23-D34E42FC9E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{4AB39424-3285-4835-8C22-5177DDC0314F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AB39424-3285-4835-8C22-5177DDC0314F}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
   <si>
     <t>Trip Type</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>whatsapp-goodie</t>
+  </si>
+  <si>
+    <t>Singapore Changi Airport Terminal 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Heathrow Airport Terminal 3, London</t>
   </si>
 </sst>
 </file>
@@ -264,8 +270,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="[$-13C09]hh:mm;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-13C09]hh:mm;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -311,13 +317,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -718,7 +723,8 @@
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.88671875" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="52.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" customWidth="1"/>
     <col min="7" max="8" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -762,7 +768,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -788,7 +794,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -909,7 +915,7 @@
       <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" t="s">
         <v>64</v>
       </c>
     </row>

--- a/Data/itinerary.xlsx
+++ b/Data/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkko\Desktop\TI xls 260529\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A288DB95-7E69-48C2-8D23-D34E42FC9E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE98370-506A-492F-ACB9-8C2FB5FD9183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AB39424-3285-4835-8C22-5177DDC0314F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4AB39424-3285-4835-8C22-5177DDC0314F}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>Trip Type</t>
   </si>
@@ -145,36 +145,24 @@
     <t>Radisson Blu</t>
   </si>
   <si>
-    <t>350 Oxford Street, WIC 1BY</t>
-  </si>
-  <si>
     <t>P2345</t>
   </si>
   <si>
     <t>Treehouse Hotel</t>
   </si>
   <si>
-    <t>14-15 Langham Place. W1B 2QS</t>
-  </si>
-  <si>
     <t>SA2222</t>
   </si>
   <si>
     <t>The Mandeville</t>
   </si>
   <si>
-    <t>Mandeville Place, W1U 2BE</t>
-  </si>
-  <si>
     <t>HS9000</t>
   </si>
   <si>
     <t>Thistle London Holborn</t>
   </si>
   <si>
-    <t>Bloomsbury Way, WC1A 2SD</t>
-  </si>
-  <si>
     <t>BSS21</t>
   </si>
   <si>
@@ -259,10 +247,34 @@
     <t>whatsapp-goodie</t>
   </si>
   <si>
-    <t>Singapore Changi Airport Terminal 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Heathrow Airport Terminal 3, London</t>
+    <t>Nelson Rd, Longford, Hounslow TW6 1QG, UK</t>
+  </si>
+  <si>
+    <t>Heathrow Airport Terminal 3</t>
+  </si>
+  <si>
+    <t>60 Airport Blvd., Singapore 819643</t>
+  </si>
+  <si>
+    <t>Singapore Airport Terminal 3</t>
+  </si>
+  <si>
+    <t>Regent street, London, UK</t>
+  </si>
+  <si>
+    <t>Carburton St, London W1W 5EE, UK</t>
+  </si>
+  <si>
+    <t>350 Oxford Street, WIC 1BY, UK</t>
+  </si>
+  <si>
+    <t>14-15 Langham Place. W1B 2QS, UK</t>
+  </si>
+  <si>
+    <t>Mandeville Place, W1U 2BE, UK</t>
+  </si>
+  <si>
+    <t>Bloomsbury Way, WC1A 2SD, UK</t>
   </si>
 </sst>
 </file>
@@ -717,18 +729,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2527889B-AAB1-4511-9E16-6D88ADAB0A42}">
-  <dimension ref="A3:H20"/>
+  <dimension ref="A3:I20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.88671875" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="52.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
     <col min="6" max="6" width="27.109375" customWidth="1"/>
     <col min="7" max="8" width="17.88671875" customWidth="1"/>
+    <col min="9" max="9" width="43.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -753,8 +766,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46174</v>
       </c>
@@ -768,7 +784,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -779,8 +795,11 @@
       <c r="H4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46178</v>
       </c>
@@ -794,7 +813,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -805,48 +824,51 @@
       <c r="H5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
     </row>
@@ -907,16 +929,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -924,19 +946,19 @@
         <v>46176</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -944,19 +966,19 @@
         <v>46177</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -964,19 +986,19 @@
         <v>46178</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1013,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799ED3C1-78F1-4221-A683-8A933C76B94F}">
-  <dimension ref="A3:F16"/>
+  <dimension ref="A3:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1021,9 +1043,10 @@
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="26.77734375" customWidth="1"/>
     <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1031,19 +1054,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46175</v>
       </c>
@@ -1051,16 +1077,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="G4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46175</v>
       </c>
@@ -1068,56 +1097,59 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
     </row>
@@ -1142,22 +1174,22 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -1165,10 +1197,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>23900222</v>
@@ -1177,13 +1209,13 @@
         <v>122233333</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1204,22 +1236,22 @@
   <sheetData>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Data/itinerary.xlsx
+++ b/Data/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkko\Desktop\TI xls 260529\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE98370-506A-492F-ACB9-8C2FB5FD9183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C27587-2FB1-44D1-8CE0-C7184250A9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4AB39424-3285-4835-8C22-5177DDC0314F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4AB39424-3285-4835-8C22-5177DDC0314F}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -247,15 +247,9 @@
     <t>whatsapp-goodie</t>
   </si>
   <si>
-    <t>Nelson Rd, Longford, Hounslow TW6 1QG, UK</t>
-  </si>
-  <si>
     <t>Heathrow Airport Terminal 3</t>
   </si>
   <si>
-    <t>60 Airport Blvd., Singapore 819643</t>
-  </si>
-  <si>
     <t>Singapore Airport Terminal 3</t>
   </si>
   <si>
@@ -268,13 +262,19 @@
     <t>350 Oxford Street, WIC 1BY, UK</t>
   </si>
   <si>
-    <t>14-15 Langham Place. W1B 2QS, UK</t>
-  </si>
-  <si>
     <t>Mandeville Place, W1U 2BE, UK</t>
   </si>
   <si>
     <t>Bloomsbury Way, WC1A 2SD, UK</t>
+  </si>
+  <si>
+    <t>60 Airport Blvd, Singapore</t>
+  </si>
+  <si>
+    <t>Nelson Rd, Longford, Hounslow, TW6 1QG, London, UK</t>
+  </si>
+  <si>
+    <t>14-15 Langham Place, W1B 2QS, UK</t>
   </si>
 </sst>
 </file>
@@ -738,7 +738,7 @@
     <col min="5" max="5" width="31.6640625" customWidth="1"/>
     <col min="6" max="6" width="27.109375" customWidth="1"/>
     <col min="7" max="8" width="17.88671875" customWidth="1"/>
-    <col min="9" max="9" width="43.44140625" customWidth="1"/>
+    <col min="9" max="9" width="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -784,7 +784,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -796,7 +796,7 @@
         <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -825,7 +825,7 @@
         <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -929,7 +929,7 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -949,7 +949,7 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -969,7 +969,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -989,7 +989,7 @@
         <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1086,7 +1086,7 @@
         <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,7 +1106,7 @@
         <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
